--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -26104,13 +26104,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O156" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R156" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.1778809170864138</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26263,10 +26263,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O157" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6180223</v>
+        <v>6180230</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -23705,13 +23705,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>52331</v>
+        <v>52531</v>
       </c>
       <c r="O140" t="n">
-        <v>52331</v>
+        <v>52531</v>
       </c>
       <c r="R140" t="n">
-        <v>192.2019153272902</v>
+        <v>192.9364776911941</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -24986,13 +24986,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O149" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R149" t="n">
-        <v>0.426914201007393</v>
+        <v>0.4447022927160344</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25145,10 +25145,10 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O150" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U150" t="inlineStr">
         <is>
@@ -25920,12 +25920,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -25950,22 +25950,22 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N155" t="n">
-        <v>5573</v>
+        <v>6543</v>
       </c>
       <c r="O155" t="n">
-        <v>5573</v>
+        <v>6543</v>
       </c>
       <c r="R155" t="n">
-        <v>20.46858027018379</v>
+        <v>5.344377410702809</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -25998,42 +25998,42 @@
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26065,12 +26065,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26104,95 +26104,81 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>10</v>
+        <v>5573</v>
       </c>
       <c r="O156" t="n">
-        <v>10</v>
+        <v>5573</v>
       </c>
       <c r="R156" t="n">
-        <v>0.1778809170864138</v>
+        <v>20.46858027018379</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -26219,7 +26205,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -26263,103 +26249,28 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O157" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0.1956690087950551</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U157" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1135</t>
         </is>
       </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>Influenza</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD157" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE157" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF157" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG157" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN157" t="b">
-        <v>1</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
@@ -26425,6 +26336,240 @@
         </is>
       </c>
       <c r="BC157" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>11</v>
+      </c>
+      <c r="O158" t="n">
+        <v>11</v>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN158" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="AT158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -26546,7 +26691,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
@@ -26556,7 +26701,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -26608,7 +26753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6180230</v>
+        <v>6186975</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -23705,13 +23705,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>52531</v>
+        <v>52611</v>
       </c>
       <c r="O140" t="n">
-        <v>52531</v>
+        <v>52611</v>
       </c>
       <c r="R140" t="n">
-        <v>192.9364776911941</v>
+        <v>193.2303026367557</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -26249,13 +26249,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="O157" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="R157" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.3557618341728275</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -26408,10 +26408,10 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="O158" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="U158" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6186975</v>
+        <v>6187064</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -23705,13 +23705,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>52611</v>
+        <v>52747</v>
       </c>
       <c r="O140" t="n">
-        <v>52611</v>
+        <v>52747</v>
       </c>
       <c r="R140" t="n">
-        <v>193.2303026367557</v>
+        <v>193.7298050442104</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -24947,12 +24947,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -24986,95 +24986,84 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>25</v>
+        <v>827013</v>
       </c>
       <c r="O149" t="n">
-        <v>25</v>
+        <v>827013</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>2</v>
       </c>
       <c r="R149" t="n">
-        <v>0.4447022927160344</v>
+        <v>58.53243355213384</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="AA149" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ149" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -25101,7 +25090,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -25150,98 +25139,23 @@
       <c r="O150" t="n">
         <v>25</v>
       </c>
+      <c r="R150" t="n">
+        <v>0.4447022927160344</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U150" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1135</t>
         </is>
       </c>
-      <c r="V150" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>Influenza</t>
-        </is>
-      </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD150" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE150" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF150" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG150" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN150" t="b">
-        <v>1</v>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
@@ -25335,17 +25249,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -25370,7 +25284,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25379,81 +25293,170 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>1384</v>
+        <v>25</v>
       </c>
       <c r="O151" t="n">
-        <v>1384</v>
-      </c>
-      <c r="R151" t="n">
-        <v>1.13046283607102</v>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN151" t="b">
+        <v>1</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
       <c r="AT151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25515,7 +25518,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -25524,13 +25527,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>1926</v>
+        <v>1384</v>
       </c>
       <c r="O152" t="n">
-        <v>1926</v>
+        <v>1384</v>
       </c>
       <c r="R152" t="n">
-        <v>1.573172992971666</v>
+        <v>1.13046283607102</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -25660,7 +25663,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -25669,13 +25672,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>2417</v>
+        <v>1926</v>
       </c>
       <c r="O153" t="n">
-        <v>2417</v>
+        <v>1926</v>
       </c>
       <c r="R153" t="n">
-        <v>1.974225921086457</v>
+        <v>1.573172992971666</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -25805,7 +25808,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -25814,13 +25817,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>4094</v>
+        <v>2417</v>
       </c>
       <c r="O154" t="n">
-        <v>4094</v>
+        <v>2417</v>
       </c>
       <c r="R154" t="n">
-        <v>3.344013620574247</v>
+        <v>1.974225921086457</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -25950,7 +25953,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -25959,13 +25962,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>6543</v>
+        <v>4094</v>
       </c>
       <c r="O155" t="n">
-        <v>6543</v>
+        <v>4094</v>
       </c>
       <c r="R155" t="n">
-        <v>5.344377410702809</v>
+        <v>3.344013620574247</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -26065,12 +26068,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26095,22 +26098,22 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N156" t="n">
-        <v>5573</v>
+        <v>6543</v>
       </c>
       <c r="O156" t="n">
-        <v>5573</v>
+        <v>6543</v>
       </c>
       <c r="R156" t="n">
-        <v>20.46858027018379</v>
+        <v>5.344377410702809</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26143,42 +26146,42 @@
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26210,12 +26213,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26249,95 +26252,81 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>20</v>
+        <v>5573</v>
       </c>
       <c r="O157" t="n">
-        <v>20</v>
+        <v>5573</v>
       </c>
       <c r="R157" t="n">
-        <v>0.3557618341728275</v>
+        <v>20.46858027018379</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -26364,7 +26353,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -26408,103 +26397,28 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="O158" t="n">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0.4447022927160344</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U158" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1135</t>
         </is>
       </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>Influenza</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE158" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF158" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG158" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN158" t="b">
-        <v>1</v>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
@@ -26570,6 +26484,240 @@
         </is>
       </c>
       <c r="BC158" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>25</v>
+      </c>
+      <c r="O159" t="n">
+        <v>25</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="AT159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -26691,7 +26839,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
@@ -26701,7 +26849,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -26753,7 +26901,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6187064</v>
+        <v>7014218</v>
       </c>
     </row>
     <row r="16">
@@ -26763,7 +26911,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -24947,12 +24947,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -24986,16 +24986,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>827013</v>
+        <v>125</v>
       </c>
       <c r="O149" t="n">
-        <v>827013</v>
-      </c>
-      <c r="Q149" t="n">
-        <v>2</v>
+        <v>125</v>
       </c>
       <c r="R149" t="n">
-        <v>58.53243355213384</v>
+        <v>1.387686535599488</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25028,42 +25025,42 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -25095,12 +25092,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25134,95 +25131,84 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>25</v>
+        <v>827013</v>
       </c>
       <c r="O150" t="n">
-        <v>25</v>
+        <v>827013</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>2</v>
       </c>
       <c r="R150" t="n">
-        <v>0.4447022927160344</v>
+        <v>58.53243355213384</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="AA150" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ150" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -25249,7 +25235,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -25298,98 +25284,23 @@
       <c r="O151" t="n">
         <v>25</v>
       </c>
+      <c r="R151" t="n">
+        <v>0.4447022927160344</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U151" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1135</t>
         </is>
       </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>Influenza</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD151" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE151" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF151" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG151" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN151" t="b">
-        <v>1</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
@@ -25483,17 +25394,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -25518,7 +25429,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -25527,81 +25438,170 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>1384</v>
+        <v>25</v>
       </c>
       <c r="O152" t="n">
-        <v>1384</v>
-      </c>
-      <c r="R152" t="n">
-        <v>1.13046283607102</v>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN152" t="b">
+        <v>1</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25663,7 +25663,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -25672,13 +25672,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>1926</v>
+        <v>1384</v>
       </c>
       <c r="O153" t="n">
-        <v>1926</v>
+        <v>1384</v>
       </c>
       <c r="R153" t="n">
-        <v>1.573172992971666</v>
+        <v>1.13046283607102</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -25817,13 +25817,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>2417</v>
+        <v>1926</v>
       </c>
       <c r="O154" t="n">
-        <v>2417</v>
+        <v>1926</v>
       </c>
       <c r="R154" t="n">
-        <v>1.974225921086457</v>
+        <v>1.573172992971666</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -25962,13 +25962,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>4094</v>
+        <v>2417</v>
       </c>
       <c r="O155" t="n">
-        <v>4094</v>
+        <v>2417</v>
       </c>
       <c r="R155" t="n">
-        <v>3.344013620574247</v>
+        <v>1.974225921086457</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -26107,13 +26107,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>6543</v>
+        <v>4094</v>
       </c>
       <c r="O156" t="n">
-        <v>6543</v>
+        <v>4094</v>
       </c>
       <c r="R156" t="n">
-        <v>5.344377410702809</v>
+        <v>3.344013620574247</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26213,12 +26213,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26243,22 +26243,22 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N157" t="n">
-        <v>5573</v>
+        <v>6543</v>
       </c>
       <c r="O157" t="n">
-        <v>5573</v>
+        <v>6543</v>
       </c>
       <c r="R157" t="n">
-        <v>20.46858027018379</v>
+        <v>5.344377410702809</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -26291,42 +26291,42 @@
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26358,12 +26358,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -26397,95 +26397,81 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>25</v>
+        <v>5573</v>
       </c>
       <c r="O158" t="n">
-        <v>25</v>
+        <v>5573</v>
       </c>
       <c r="R158" t="n">
-        <v>0.4447022927160344</v>
+        <v>20.46858027018379</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26498,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -26561,98 +26547,23 @@
       <c r="O159" t="n">
         <v>25</v>
       </c>
+      <c r="R159" t="n">
+        <v>0.4447022927160344</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U159" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1135</t>
         </is>
       </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1135</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>Influenza</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE159" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG159" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN159" t="b">
-        <v>1</v>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
@@ -26718,6 +26629,240 @@
         </is>
       </c>
       <c r="BC159" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>25</v>
+      </c>
+      <c r="O160" t="n">
+        <v>25</v>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN160" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="AT160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -26839,7 +26984,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
@@ -26849,7 +26994,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -26901,7 +27046,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7014218</v>
+        <v>7014343</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -23705,13 +23705,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>52747</v>
+        <v>52791</v>
       </c>
       <c r="O140" t="n">
-        <v>52747</v>
+        <v>52791</v>
       </c>
       <c r="R140" t="n">
-        <v>193.7298050442104</v>
+        <v>193.8914087642692</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7014343</v>
+        <v>7014387</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -23705,13 +23705,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>52791</v>
+        <v>52828</v>
       </c>
       <c r="O140" t="n">
-        <v>52791</v>
+        <v>52828</v>
       </c>
       <c r="R140" t="n">
-        <v>193.8914087642692</v>
+        <v>194.0273028015915</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7014387</v>
+        <v>7014424</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -23705,13 +23705,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>52828</v>
+        <v>52829</v>
       </c>
       <c r="O140" t="n">
-        <v>52828</v>
+        <v>52829</v>
       </c>
       <c r="R140" t="n">
-        <v>194.0273028015915</v>
+        <v>194.030975613411</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -26542,13 +26542,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="O159" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="R159" t="n">
-        <v>0.4447022927160344</v>
+        <v>0.6047951180938068</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -26701,10 +26701,10 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="O160" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="U160" t="inlineStr">
         <is>
@@ -26865,6 +26865,151 @@
       <c r="BC160" t="inlineStr">
         <is>
           <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>12299</v>
+      </c>
+      <c r="O161" t="n">
+        <v>12299</v>
+      </c>
+      <c r="R161" t="n">
+        <v>10.04592660465136</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26901,7 +27046,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -26984,7 +27129,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -26994,7 +27139,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -27046,7 +27191,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7014424</v>
+        <v>7026733</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -24986,13 +24986,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O149" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="R149" t="n">
-        <v>1.387686535599488</v>
+        <v>1.432092504738672</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7026733</v>
+        <v>7026737</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -26542,13 +26542,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="O159" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R159" t="n">
-        <v>0.6047951180938068</v>
+        <v>0.6937355766370136</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -26701,10 +26701,10 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="O160" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="U160" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7026737</v>
+        <v>7026742</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -21013,13 +21013,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>20715</v>
+        <v>20716</v>
       </c>
       <c r="O122" t="n">
-        <v>20715</v>
+        <v>20716</v>
       </c>
       <c r="R122" t="n">
-        <v>76.08229684135244</v>
+        <v>76.08596965317197</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -23705,13 +23705,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>52829</v>
+        <v>53002</v>
       </c>
       <c r="O140" t="n">
-        <v>52829</v>
+        <v>53002</v>
       </c>
       <c r="R140" t="n">
-        <v>194.030975613411</v>
+        <v>194.6663720581879</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7026742</v>
+        <v>7026916</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -23705,13 +23705,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>53002</v>
+        <v>53030</v>
       </c>
       <c r="O140" t="n">
-        <v>53002</v>
+        <v>53030</v>
       </c>
       <c r="R140" t="n">
-        <v>194.6663720581879</v>
+        <v>194.7692107891345</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7026916</v>
+        <v>7026944</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -21013,13 +21013,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>20716</v>
+        <v>20717</v>
       </c>
       <c r="O122" t="n">
-        <v>20716</v>
+        <v>20717</v>
       </c>
       <c r="R122" t="n">
-        <v>76.08596965317197</v>
+        <v>76.08964246499148</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -23705,13 +23705,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>53030</v>
+        <v>53036</v>
       </c>
       <c r="O140" t="n">
-        <v>53030</v>
+        <v>53036</v>
       </c>
       <c r="R140" t="n">
-        <v>194.7692107891345</v>
+        <v>194.7912476600516</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -26542,13 +26542,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="O159" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="R159" t="n">
-        <v>0.6937355766370136</v>
+        <v>0.9605569522666343</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -26701,10 +26701,10 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="O160" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="U160" t="inlineStr">
         <is>
@@ -27008,6 +27008,151 @@
         </is>
       </c>
       <c r="BC161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>20697</v>
+      </c>
+      <c r="O162" t="n">
+        <v>20697</v>
+      </c>
+      <c r="R162" t="n">
+        <v>16.90548361138866</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -27046,7 +27191,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -27129,7 +27274,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
@@ -27139,7 +27284,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
@@ -27191,7 +27336,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7026944</v>
+        <v>7047663</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -31790,13 +31790,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>53036</v>
+        <v>53055</v>
       </c>
       <c r="O182" t="n">
-        <v>53036</v>
+        <v>53055</v>
       </c>
       <c r="R182" t="n">
-        <v>194.7912476600516</v>
+        <v>194.8610310846225</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -37177,13 +37177,13 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>5573</v>
+        <v>70384</v>
       </c>
       <c r="O214" t="n">
-        <v>5573</v>
+        <v>70384</v>
       </c>
       <c r="R214" t="n">
-        <v>20.46858027018379</v>
+        <v>258.5071871050809</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -37322,13 +37322,13 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="O215" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="R215" t="n">
-        <v>0.9605569522666343</v>
+        <v>1.102861685935765</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -37481,10 +37481,10 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="O216" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="U216" t="inlineStr">
         <is>
@@ -37935,6 +37935,544 @@
       <c r="BC218" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>31428</v>
+      </c>
+      <c r="O219" t="n">
+        <v>31428</v>
+      </c>
+      <c r="R219" t="n">
+        <v>25.6706546329769</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr"/>
+      <c r="AT219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV219" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA219" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB219" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC219" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>0</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP220" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="AT220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU220" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV220" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA220" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB220" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC220" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use reported influenza total; Influenza A and B child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN221" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP221" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1135</t>
+        </is>
+      </c>
+      <c r="AT221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU221" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV221" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA221" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB221" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC221" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -37971,7 +38509,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -38054,7 +38592,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10">
@@ -38064,7 +38602,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11">
@@ -38084,7 +38622,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
@@ -38116,7 +38654,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8546668</v>
+        <v>8642934</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -31790,13 +31790,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>53055</v>
+        <v>53061</v>
       </c>
       <c r="O182" t="n">
-        <v>53055</v>
+        <v>53061</v>
       </c>
       <c r="R182" t="n">
-        <v>194.8610310846225</v>
+        <v>194.8830679555396</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -37177,13 +37177,13 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>70384</v>
+        <v>70845</v>
       </c>
       <c r="O214" t="n">
-        <v>70384</v>
+        <v>70845</v>
       </c>
       <c r="R214" t="n">
-        <v>258.5071871050809</v>
+        <v>260.2003533538796</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8642934</v>
+        <v>8643401</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -37322,13 +37322,13 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O215" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R215" t="n">
-        <v>1.102861685935765</v>
+        <v>1.156225961061689</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -37481,10 +37481,10 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O216" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="U216" t="inlineStr">
         <is>
@@ -38150,13 +38150,13 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O220" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O221" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U221" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8643401</v>
+        <v>8643407</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -50402,13 +50402,13 @@
         </is>
       </c>
       <c r="N288" t="n">
-        <v>71017</v>
+        <v>71023</v>
       </c>
       <c r="O288" t="n">
-        <v>71017</v>
+        <v>71023</v>
       </c>
       <c r="R288" t="n">
-        <v>260.832076986837</v>
+        <v>260.8541138577541</v>
       </c>
       <c r="S288" t="inlineStr">
         <is>
@@ -54361,13 +54361,13 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O311" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="R311" t="n">
-        <v>0.569218934676524</v>
+        <v>0.6759474849283722</v>
       </c>
       <c r="S311" t="inlineStr">
         <is>
@@ -54520,10 +54520,10 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O312" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="U312" t="inlineStr">
         <is>
@@ -54865,7 +54865,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8781271</v>
+        <v>8781283</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d038/2026-2029.xlsx
+++ b/diseases/d038/2026-2029.xlsx
@@ -42896,13 +42896,13 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>53063</v>
+        <v>53064</v>
       </c>
       <c r="O246" t="n">
-        <v>53063</v>
+        <v>53064</v>
       </c>
       <c r="R246" t="n">
-        <v>194.8904135791786</v>
+        <v>194.8940863909982</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -50402,13 +50402,13 @@
         </is>
       </c>
       <c r="N288" t="n">
-        <v>71023</v>
+        <v>71053</v>
       </c>
       <c r="O288" t="n">
-        <v>71023</v>
+        <v>71053</v>
       </c>
       <c r="R288" t="n">
-        <v>260.8541138577541</v>
+        <v>260.9642982123397</v>
       </c>
       <c r="S288" t="inlineStr">
         <is>
@@ -54361,13 +54361,13 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O311" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R311" t="n">
-        <v>0.6759474849283722</v>
+        <v>0.8182522185975032</v>
       </c>
       <c r="S311" t="inlineStr">
         <is>
@@ -54520,10 +54520,10 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O312" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="U312" t="inlineStr">
         <is>
@@ -54684,6 +54684,151 @@
       <c r="BC312" t="inlineStr">
         <is>
           <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>influenza</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N313" t="n">
+        <v>42320</v>
+      </c>
+      <c r="O313" t="n">
+        <v>42320</v>
+      </c>
+      <c r="R313" t="n">
+        <v>34.56733180818323</v>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO313" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP313" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR313" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS313" t="inlineStr"/>
+      <c r="AT313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU313" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV313" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW313" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX313" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY313" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA313" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB313" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC313" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -54720,7 +54865,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -54803,7 +54948,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -54813,7 +54958,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -54865,7 +55010,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8781283</v>
+        <v>8823642</v>
       </c>
     </row>
     <row r="16">
